--- a/data collection/cv-variances.xlsx
+++ b/data collection/cv-variances.xlsx
@@ -5,37 +5,25 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/medina_colabrese_epfl_ch/Documents/0 Mobile Robots/EPFL-BOMR-Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/medina_colabrese_epfl_ch/Documents/0 Mobile Robots/EPFL-BOMR-Project/data collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="8_{4252B687-B2B9-4B78-BAD3-7C2B897D982E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DF33EBD-3399-49BC-844B-D8F17CA4423B}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="8_{4252B687-B2B9-4B78-BAD3-7C2B897D982E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD1DF043-B060-460B-84A0-E1C69706D927}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{7C74CB82-38BE-4B9F-9BE2-E33ADDF44A6B}"/>
+    <workbookView xWindow="5508" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{7C74CB82-38BE-4B9F-9BE2-E33ADDF44A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$F$2:$F$272</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!#REF!</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!#REF!</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$E$1:$E$272</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$F$1:$F$272</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$E$2:$E$272</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$E$193:$E$272</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$F$2:$F$272</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$E$193:$E$272</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!#REF!</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$E$1:$E$272</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$L$1</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$L$2:$L$272</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$L$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$L$2:$L$272</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$E$2:$E$272</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$L$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$L$2:$L$272</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$F$2:$F$272</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,15 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>x</t>
   </si>
   <si>
     <t>y</t>
-  </si>
-  <si>
-    <t>papers</t>
   </si>
   <si>
     <t>actual</t>
@@ -76,12 +61,6 @@
   </si>
   <si>
     <t>theta</t>
-  </si>
-  <si>
-    <t>measured - raw</t>
-  </si>
-  <si>
-    <t>measured - adjusted</t>
   </si>
   <si>
     <t>degrees</t>
@@ -164,11 +143,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -192,7 +168,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -200,7 +176,7 @@
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
         <cx:txData>
-          <cx:v>theta</cx:v>
+          <cx:v>Theta Positional Error (CV)</cx:v>
         </cx:txData>
       </cx:tx>
       <cx:txPr>
@@ -220,7 +196,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
             </a:rPr>
-            <a:t>theta</a:t>
+            <a:t>Theta Positional Error (CV)</a:t>
           </a:r>
         </a:p>
       </cx:txPr>
@@ -230,7 +206,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{B3BDD736-8B67-45AD-90F7-29B74469BE70}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v/>
             </cx:txData>
           </cx:tx>
@@ -244,10 +220,67 @@
       </cx:plotAreaRegion>
       <cx:axis id="0">
         <cx:catScaling gapWidth="0"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Error range [rad]</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Error range [rad]</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:tickLabels/>
+        <cx:numFmt formatCode="#,##0.00" sourceLinked="0"/>
       </cx:axis>
       <cx:axis id="1">
         <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Count</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Count</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:majorGridlines/>
         <cx:tickLabels/>
       </cx:axis>
@@ -261,18 +294,45 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.15</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>X Positional Error (CV)</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>X Positional Error (CV)</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{88044D45-8198-4342-BA2D-F14EDD308539}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>x error</cx:v>
             </cx:txData>
           </cx:tx>
@@ -284,10 +344,67 @@
       </cx:plotAreaRegion>
       <cx:axis id="0">
         <cx:catScaling gapWidth="0"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Error range [mm]</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Error range [mm]</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:tickLabels/>
+        <cx:numFmt formatCode="#,##0.00" sourceLinked="0"/>
       </cx:axis>
       <cx:axis id="1">
         <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Count</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Count</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:majorGridlines/>
         <cx:tickLabels/>
       </cx:axis>
@@ -301,18 +418,45 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Y Positional Error (CV)</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Y Positional Error (CV)</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{1A0CF01A-119D-4FC0-A817-FC8A22F16E8C}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>y error</cx:v>
             </cx:txData>
           </cx:tx>
@@ -324,10 +468,67 @@
       </cx:plotAreaRegion>
       <cx:axis id="0">
         <cx:catScaling gapWidth="0"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Error range [mm]</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Error range [mm]</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:tickLabels/>
+        <cx:numFmt formatCode="#,##0.00" sourceLinked="0"/>
       </cx:axis>
       <cx:axis id="1">
         <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Count</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Count</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
         <cx:majorGridlines/>
         <cx:tickLabels/>
       </cx:axis>
@@ -1984,16 +2185,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>116205</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>243539</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>558165</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>116205</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>425116</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>14505</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2029,8 +2230,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6227445" y="2127885"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="20777434" y="530493"/>
+              <a:ext cx="5315050" cy="3911633"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2062,16 +2263,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>348716</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>145881</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>424815</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>170548</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>159217</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2107,8 +2308,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="973455" y="306705"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="9973979" y="883818"/>
+              <a:ext cx="5596990" cy="3887504"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2140,16 +2341,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>382905</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>253365</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>474345</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>200527</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2185,8 +2386,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1663065" y="3453765"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="15653786" y="530892"/>
+              <a:ext cx="5080636" cy="3904348"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2540,33 +2741,33 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -2590,17 +2791,17 @@
         <f>B2-D2</f>
         <v>-1.1260375976560226</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>15</v>
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="P2" t="s">
         <v>0</v>
@@ -2642,7 +2843,7 @@
         <v>-4.3450895391530797E-2</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <f>I3-J3</f>
@@ -2692,7 +2893,7 @@
         <v>4.39277670768898E-2</v>
       </c>
       <c r="P4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4">
         <f>VAR(L3:L272)</f>
@@ -5865,7 +6066,7 @@
         <v>-0.36144089089355202</v>
       </c>
       <c r="K92" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L92">
         <f t="shared" si="6"/>
@@ -9108,7 +9309,7 @@
         <v>-0.36144089089355202</v>
       </c>
       <c r="K182" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L182">
         <f t="shared" si="9"/>
@@ -11259,5224 +11460,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFC8AC2-9CC8-47A0-9071-4711FF72AFF5}">
-  <dimension ref="A1:F191"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1">
-        <v>48</v>
-      </c>
-      <c r="B1">
-        <v>48</v>
-      </c>
-      <c r="C1">
-        <v>47.507534027099602</v>
-      </c>
-      <c r="D1">
-        <v>49.052055358886697</v>
-      </c>
-      <c r="E1">
-        <f>A1-C1</f>
-        <v>0.49246597290039773</v>
-      </c>
-      <c r="F1">
-        <f>B1-D1</f>
-        <v>-1.0520553588866974</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>48</v>
-      </c>
-      <c r="B2">
-        <v>48</v>
-      </c>
-      <c r="C2">
-        <v>47.659088134765597</v>
-      </c>
-      <c r="D2">
-        <v>49.101795196533203</v>
-      </c>
-      <c r="E2">
-        <f>A2-C2</f>
-        <v>0.34091186523440342</v>
-      </c>
-      <c r="F2">
-        <f>B2-D2</f>
-        <v>-1.1017951965332031</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>48</v>
-      </c>
-      <c r="B3">
-        <v>48</v>
-      </c>
-      <c r="C3">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D3">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E3">
-        <f>A3-C3</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F3">
-        <f>B3-D3</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>48</v>
-      </c>
-      <c r="B4">
-        <v>48</v>
-      </c>
-      <c r="C4">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D4">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E4">
-        <f>A4-C4</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F4">
-        <f>B4-D4</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>48</v>
-      </c>
-      <c r="B5">
-        <v>48</v>
-      </c>
-      <c r="C5">
-        <v>47.6985664367675</v>
-      </c>
-      <c r="D5">
-        <v>49.139938354492102</v>
-      </c>
-      <c r="E5">
-        <f>A5-C5</f>
-        <v>0.30143356323250003</v>
-      </c>
-      <c r="F5">
-        <f>B5-D5</f>
-        <v>-1.1399383544921022</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>48</v>
-      </c>
-      <c r="B6">
-        <v>48</v>
-      </c>
-      <c r="C6">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D6">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E6">
-        <f>A6-C6</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F6">
-        <f>B6-D6</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>48</v>
-      </c>
-      <c r="B7">
-        <v>48</v>
-      </c>
-      <c r="C7">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D7">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E7">
-        <f>A7-C7</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F7">
-        <f>B7-D7</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>48</v>
-      </c>
-      <c r="B8">
-        <v>48</v>
-      </c>
-      <c r="C8">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D8">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E8">
-        <f>A8-C8</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F8">
-        <f>B8-D8</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>48</v>
-      </c>
-      <c r="B9">
-        <v>48</v>
-      </c>
-      <c r="C9">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D9">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E9">
-        <f>A9-C9</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F9">
-        <f>B9-D9</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>48</v>
-      </c>
-      <c r="B10">
-        <v>48</v>
-      </c>
-      <c r="C10">
-        <v>47.753200531005803</v>
-      </c>
-      <c r="D10">
-        <v>49.176170349121001</v>
-      </c>
-      <c r="E10">
-        <f>A10-C10</f>
-        <v>0.24679946899419747</v>
-      </c>
-      <c r="F10">
-        <f>B10-D10</f>
-        <v>-1.1761703491210014</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>48</v>
-      </c>
-      <c r="B11">
-        <v>48</v>
-      </c>
-      <c r="C11">
-        <v>47.606349945068303</v>
-      </c>
-      <c r="D11">
-        <v>49.007598876953097</v>
-      </c>
-      <c r="E11">
-        <f>A11-C11</f>
-        <v>0.39365005493169747</v>
-      </c>
-      <c r="F11">
-        <f>B11-D11</f>
-        <v>-1.0075988769530966</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>48</v>
-      </c>
-      <c r="B12">
-        <v>48</v>
-      </c>
-      <c r="C12">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D12">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E12">
-        <f>A12-C12</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F12">
-        <f>B12-D12</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>48</v>
-      </c>
-      <c r="B13">
-        <v>48</v>
-      </c>
-      <c r="C13">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D13">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E13">
-        <f>A13-C13</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F13">
-        <f>B13-D13</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>48</v>
-      </c>
-      <c r="B14">
-        <v>48</v>
-      </c>
-      <c r="C14">
-        <v>47.609687805175703</v>
-      </c>
-      <c r="D14">
-        <v>49.049201965332003</v>
-      </c>
-      <c r="E14">
-        <f>A14-C14</f>
-        <v>0.39031219482429691</v>
-      </c>
-      <c r="F14">
-        <f>B14-D14</f>
-        <v>-1.0492019653320028</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>48</v>
-      </c>
-      <c r="B15">
-        <v>48</v>
-      </c>
-      <c r="C15">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D15">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E15">
-        <f>A15-C15</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F15">
-        <f>B15-D15</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>48</v>
-      </c>
-      <c r="B16">
-        <v>48</v>
-      </c>
-      <c r="C16">
-        <v>47.594608306884702</v>
-      </c>
-      <c r="D16">
-        <v>49.051139831542898</v>
-      </c>
-      <c r="E16">
-        <f>A16-C16</f>
-        <v>0.40539169311529832</v>
-      </c>
-      <c r="F16">
-        <f>B16-D16</f>
-        <v>-1.0511398315428977</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>48</v>
-      </c>
-      <c r="B17">
-        <v>48</v>
-      </c>
-      <c r="C17">
-        <v>47.609687805175703</v>
-      </c>
-      <c r="D17">
-        <v>49.049201965332003</v>
-      </c>
-      <c r="E17">
-        <f>A17-C17</f>
-        <v>0.39031219482429691</v>
-      </c>
-      <c r="F17">
-        <f>B17-D17</f>
-        <v>-1.0492019653320028</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>48</v>
-      </c>
-      <c r="B18">
-        <v>48</v>
-      </c>
-      <c r="C18">
-        <v>47.606796264648402</v>
-      </c>
-      <c r="D18">
-        <v>49.064842224121001</v>
-      </c>
-      <c r="E18">
-        <f>A18-C18</f>
-        <v>0.39320373535159803</v>
-      </c>
-      <c r="F18">
-        <f>B18-D18</f>
-        <v>-1.0648422241210014</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>48</v>
-      </c>
-      <c r="C19">
-        <v>47.823360443115199</v>
-      </c>
-      <c r="D19">
-        <v>49.017951965332003</v>
-      </c>
-      <c r="E19">
-        <f>A19-C19</f>
-        <v>0.17663955688480115</v>
-      </c>
-      <c r="F19">
-        <f>B19-D19</f>
-        <v>-1.0179519653320028</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>48</v>
-      </c>
-      <c r="B20">
-        <v>48</v>
-      </c>
-      <c r="C20">
-        <v>48.4497871398925</v>
-      </c>
-      <c r="D20">
-        <v>47.599956512451101</v>
-      </c>
-      <c r="E20">
-        <f>A20-C20</f>
-        <v>-0.44978713989249997</v>
-      </c>
-      <c r="F20">
-        <f>B20-D20</f>
-        <v>0.40004348754889918</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>48</v>
-      </c>
-      <c r="B21">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D21">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E21">
-        <f>A21-C21</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F21">
-        <f>B21-D21</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>48</v>
-      </c>
-      <c r="B22">
-        <v>48</v>
-      </c>
-      <c r="C22">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D22">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E22">
-        <f>A22-C22</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F22">
-        <f>B22-D22</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>48</v>
-      </c>
-      <c r="B23">
-        <v>48</v>
-      </c>
-      <c r="C23">
-        <v>48.309028625488203</v>
-      </c>
-      <c r="D23">
-        <v>48.258491516113203</v>
-      </c>
-      <c r="E23">
-        <f>A23-C23</f>
-        <v>-0.30902862548820309</v>
-      </c>
-      <c r="F23">
-        <f>B23-D23</f>
-        <v>-0.25849151611320309</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>48</v>
-      </c>
-      <c r="B24">
-        <v>48</v>
-      </c>
-      <c r="C24">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D24">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E24">
-        <f>A24-C24</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F24">
-        <f>B24-D24</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>48</v>
-      </c>
-      <c r="B25">
-        <v>48</v>
-      </c>
-      <c r="C25">
-        <v>47.648563385009702</v>
-      </c>
-      <c r="D25">
-        <v>49.1797485351562</v>
-      </c>
-      <c r="E25">
-        <f>A25-C25</f>
-        <v>0.35143661499029832</v>
-      </c>
-      <c r="F25">
-        <f>B25-D25</f>
-        <v>-1.1797485351562003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>48</v>
-      </c>
-      <c r="C26">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D26">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E26">
-        <f>A26-C26</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F26">
-        <f>B26-D26</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>48</v>
-      </c>
-      <c r="B27">
-        <v>48</v>
-      </c>
-      <c r="C27">
-        <v>47.5992622375488</v>
-      </c>
-      <c r="D27">
-        <v>49.127159118652301</v>
-      </c>
-      <c r="E27">
-        <f>A27-C27</f>
-        <v>0.4007377624512003</v>
-      </c>
-      <c r="F27">
-        <f>B27-D27</f>
-        <v>-1.1271591186523011</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>48</v>
-      </c>
-      <c r="B28">
-        <v>48</v>
-      </c>
-      <c r="C28">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D28">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E28">
-        <f>A28-C28</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F28">
-        <f>B28-D28</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29">
-        <v>48</v>
-      </c>
-      <c r="B29">
-        <v>48</v>
-      </c>
-      <c r="C29">
-        <v>47.559135437011697</v>
-      </c>
-      <c r="D29">
-        <v>49.286468505859297</v>
-      </c>
-      <c r="E29">
-        <f>A29-C29</f>
-        <v>0.44086456298830257</v>
-      </c>
-      <c r="F29">
-        <f>B29-D29</f>
-        <v>-1.2864685058592968</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30">
-        <v>48</v>
-      </c>
-      <c r="B30">
-        <v>48</v>
-      </c>
-      <c r="C30">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D30">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E30">
-        <f>A30-C30</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F30">
-        <f>B30-D30</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31">
-        <v>48</v>
-      </c>
-      <c r="B31">
-        <v>48</v>
-      </c>
-      <c r="C31">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D31">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E31">
-        <f>A31-C31</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F31">
-        <f>B31-D31</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
-        <v>48</v>
-      </c>
-      <c r="B32">
-        <v>48</v>
-      </c>
-      <c r="C32">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D32">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E32">
-        <f>A32-C32</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F32">
-        <f>B32-D32</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>48</v>
-      </c>
-      <c r="B33">
-        <v>48</v>
-      </c>
-      <c r="C33">
-        <v>48.356559753417898</v>
-      </c>
-      <c r="D33">
-        <v>47.525215148925703</v>
-      </c>
-      <c r="E33">
-        <f>A33-C33</f>
-        <v>-0.3565597534178977</v>
-      </c>
-      <c r="F33">
-        <f>B33-D33</f>
-        <v>0.47478485107429691</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
-        <v>48</v>
-      </c>
-      <c r="B34">
-        <v>48</v>
-      </c>
-      <c r="C34">
-        <v>47.596893310546797</v>
-      </c>
-      <c r="D34">
-        <v>49.0504150390625</v>
-      </c>
-      <c r="E34">
-        <f>A34-C34</f>
-        <v>0.40310668945320316</v>
-      </c>
-      <c r="F34">
-        <f>B34-D34</f>
-        <v>-1.0504150390625</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35">
-        <v>48</v>
-      </c>
-      <c r="B35">
-        <v>48</v>
-      </c>
-      <c r="C35">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D35">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E35">
-        <f>A35-C35</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F35">
-        <f>B35-D35</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36">
-        <v>48</v>
-      </c>
-      <c r="B36">
-        <v>48</v>
-      </c>
-      <c r="C36">
-        <v>47.508544921875</v>
-      </c>
-      <c r="D36">
-        <v>49.016983032226499</v>
-      </c>
-      <c r="E36">
-        <f>A36-C36</f>
-        <v>0.491455078125</v>
-      </c>
-      <c r="F36">
-        <f>B36-D36</f>
-        <v>-1.0169830322264986</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
-        <v>48</v>
-      </c>
-      <c r="B37">
-        <v>48</v>
-      </c>
-      <c r="C37">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D37">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E37">
-        <f>A37-C37</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F37">
-        <f>B37-D37</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
-        <v>48</v>
-      </c>
-      <c r="B38">
-        <v>48</v>
-      </c>
-      <c r="C38">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D38">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E38">
-        <f>A38-C38</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F38">
-        <f>B38-D38</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39">
-        <v>48</v>
-      </c>
-      <c r="B39">
-        <v>48</v>
-      </c>
-      <c r="C39">
-        <v>47.873001098632798</v>
-      </c>
-      <c r="D39">
-        <v>49.070487976074197</v>
-      </c>
-      <c r="E39">
-        <f>A39-C39</f>
-        <v>0.12699890136720171</v>
-      </c>
-      <c r="F39">
-        <f>B39-D39</f>
-        <v>-1.0704879760741974</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
-        <v>48</v>
-      </c>
-      <c r="B40">
-        <v>48</v>
-      </c>
-      <c r="C40">
-        <v>47.609687805175703</v>
-      </c>
-      <c r="D40">
-        <v>49.049201965332003</v>
-      </c>
-      <c r="E40">
-        <f>A40-C40</f>
-        <v>0.39031219482429691</v>
-      </c>
-      <c r="F40">
-        <f>B40-D40</f>
-        <v>-1.0492019653320028</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
-        <v>48</v>
-      </c>
-      <c r="B41">
-        <v>48</v>
-      </c>
-      <c r="C41">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D41">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E41">
-        <f>A41-C41</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F41">
-        <f>B41-D41</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
-        <v>48</v>
-      </c>
-      <c r="B42">
-        <v>48</v>
-      </c>
-      <c r="C42">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D42">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E42">
-        <f>A42-C42</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F42">
-        <f>B42-D42</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
-        <v>48</v>
-      </c>
-      <c r="B43">
-        <v>48</v>
-      </c>
-      <c r="C43">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D43">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E43">
-        <f>A43-C43</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F43">
-        <f>B43-D43</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
-        <v>48</v>
-      </c>
-      <c r="B44">
-        <v>48</v>
-      </c>
-      <c r="C44">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D44">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E44">
-        <f>A44-C44</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F44">
-        <f>B44-D44</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45">
-        <v>48</v>
-      </c>
-      <c r="B45">
-        <v>48</v>
-      </c>
-      <c r="C45">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D45">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E45">
-        <f>A45-C45</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F45">
-        <f>B45-D45</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46">
-        <v>48</v>
-      </c>
-      <c r="B46">
-        <v>48</v>
-      </c>
-      <c r="C46">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D46">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E46">
-        <f>A46-C46</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F46">
-        <f>B46-D46</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47">
-        <v>48</v>
-      </c>
-      <c r="B47">
-        <v>48</v>
-      </c>
-      <c r="C47">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D47">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E47">
-        <f>A47-C47</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F47">
-        <f>B47-D47</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48">
-        <v>48</v>
-      </c>
-      <c r="B48">
-        <v>48</v>
-      </c>
-      <c r="C48">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D48">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E48">
-        <f>A48-C48</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F48">
-        <f>B48-D48</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>48</v>
-      </c>
-      <c r="C49">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D49">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E49">
-        <f>A49-C49</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F49">
-        <f>B49-D49</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>48</v>
-      </c>
-      <c r="C50">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D50">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E50">
-        <f>A50-C50</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F50">
-        <f>B50-D50</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51">
-        <v>48</v>
-      </c>
-      <c r="B51">
-        <v>48</v>
-      </c>
-      <c r="C51">
-        <v>47.915611267089801</v>
-      </c>
-      <c r="D51">
-        <v>49.093227386474602</v>
-      </c>
-      <c r="E51">
-        <f>A51-C51</f>
-        <v>8.4388732910198883E-2</v>
-      </c>
-      <c r="F51">
-        <f>B51-D51</f>
-        <v>-1.0932273864746023</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <v>48</v>
-      </c>
-      <c r="C52">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D52">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E52">
-        <f>A52-C52</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F52">
-        <f>B52-D52</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53">
-        <v>48</v>
-      </c>
-      <c r="B53">
-        <v>48</v>
-      </c>
-      <c r="C53">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D53">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E53">
-        <f>A53-C53</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F53">
-        <f>B53-D53</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54">
-        <v>48</v>
-      </c>
-      <c r="B54">
-        <v>48</v>
-      </c>
-      <c r="C54">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D54">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E54">
-        <f>A54-C54</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F54">
-        <f>B54-D54</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55">
-        <v>48</v>
-      </c>
-      <c r="B55">
-        <v>48</v>
-      </c>
-      <c r="C55">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D55">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E55">
-        <f>A55-C55</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F55">
-        <f>B55-D55</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56">
-        <v>48</v>
-      </c>
-      <c r="B56">
-        <v>48</v>
-      </c>
-      <c r="C56">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D56">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E56">
-        <f>A56-C56</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F56">
-        <f>B56-D56</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57">
-        <v>48</v>
-      </c>
-      <c r="B57">
-        <v>48</v>
-      </c>
-      <c r="C57">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D57">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E57">
-        <f>A57-C57</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F57">
-        <f>B57-D57</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58">
-        <v>48</v>
-      </c>
-      <c r="B58">
-        <v>48</v>
-      </c>
-      <c r="C58">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D58">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E58">
-        <f>A58-C58</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F58">
-        <f>B58-D58</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59">
-        <v>48</v>
-      </c>
-      <c r="B59">
-        <v>48</v>
-      </c>
-      <c r="C59">
-        <v>47.609687805175703</v>
-      </c>
-      <c r="D59">
-        <v>49.049201965332003</v>
-      </c>
-      <c r="E59">
-        <f>A59-C59</f>
-        <v>0.39031219482429691</v>
-      </c>
-      <c r="F59">
-        <f>B59-D59</f>
-        <v>-1.0492019653320028</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60">
-        <v>48</v>
-      </c>
-      <c r="B60">
-        <v>48</v>
-      </c>
-      <c r="C60">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D60">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E60">
-        <f>A60-C60</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F60">
-        <f>B60-D60</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61">
-        <v>48</v>
-      </c>
-      <c r="B61">
-        <v>48</v>
-      </c>
-      <c r="C61">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D61">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E61">
-        <f>A61-C61</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F61">
-        <f>B61-D61</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62">
-        <v>48</v>
-      </c>
-      <c r="B62">
-        <v>48</v>
-      </c>
-      <c r="C62">
-        <v>47.332382202148402</v>
-      </c>
-      <c r="D62">
-        <v>49.322669982910099</v>
-      </c>
-      <c r="E62">
-        <f>A62-C62</f>
-        <v>0.66761779785159803</v>
-      </c>
-      <c r="F62">
-        <f>B62-D62</f>
-        <v>-1.3226699829100994</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63">
-        <v>48</v>
-      </c>
-      <c r="B63">
-        <v>48</v>
-      </c>
-      <c r="C63">
-        <v>48.014530181884702</v>
-      </c>
-      <c r="D63">
-        <v>49.141036987304602</v>
-      </c>
-      <c r="E63">
-        <f>A63-C63</f>
-        <v>-1.4530181884701676E-2</v>
-      </c>
-      <c r="F63">
-        <f>B63-D63</f>
-        <v>-1.1410369873046022</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64">
-        <v>48</v>
-      </c>
-      <c r="B64">
-        <v>48</v>
-      </c>
-      <c r="C64">
-        <v>47.382705688476499</v>
-      </c>
-      <c r="D64">
-        <v>49.081470489501903</v>
-      </c>
-      <c r="E64">
-        <f>A64-C64</f>
-        <v>0.61729431152350145</v>
-      </c>
-      <c r="F64">
-        <f>B64-D64</f>
-        <v>-1.0814704895019034</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65">
-        <v>48</v>
-      </c>
-      <c r="B65">
-        <v>48</v>
-      </c>
-      <c r="C65">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D65">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E65">
-        <f>A65-C65</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F65">
-        <f>B65-D65</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66">
-        <v>48</v>
-      </c>
-      <c r="B66">
-        <v>48</v>
-      </c>
-      <c r="C66">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D66">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E66">
-        <f>A66-C66</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F66">
-        <f>B66-D66</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67">
-        <v>48</v>
-      </c>
-      <c r="B67">
-        <v>48</v>
-      </c>
-      <c r="C67">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D67">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E67">
-        <f>A67-C67</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F67">
-        <f>B67-D67</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68">
-        <v>48</v>
-      </c>
-      <c r="B68">
-        <v>48</v>
-      </c>
-      <c r="C68">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D68">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E68">
-        <f>A68-C68</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F68">
-        <f>B68-D68</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69">
-        <v>48</v>
-      </c>
-      <c r="B69">
-        <v>48</v>
-      </c>
-      <c r="C69">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D69">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E69">
-        <f>A69-C69</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F69">
-        <f>B69-D69</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70">
-        <v>48</v>
-      </c>
-      <c r="B70">
-        <v>48</v>
-      </c>
-      <c r="C70">
-        <v>47.557449340820298</v>
-      </c>
-      <c r="D70">
-        <v>49.012290954589801</v>
-      </c>
-      <c r="E70">
-        <f>A70-C70</f>
-        <v>0.44255065917970171</v>
-      </c>
-      <c r="F70">
-        <f>B70-D70</f>
-        <v>-1.0122909545898011</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71">
-        <v>48</v>
-      </c>
-      <c r="B71">
-        <v>48</v>
-      </c>
-      <c r="C71">
-        <v>47.649173736572202</v>
-      </c>
-      <c r="D71">
-        <v>49.087348937988203</v>
-      </c>
-      <c r="E71">
-        <f>A71-C71</f>
-        <v>0.35082626342779832</v>
-      </c>
-      <c r="F71">
-        <f>B71-D71</f>
-        <v>-1.0873489379882031</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72">
-        <v>48</v>
-      </c>
-      <c r="B72">
-        <v>48</v>
-      </c>
-      <c r="C72">
-        <v>47.596893310546797</v>
-      </c>
-      <c r="D72">
-        <v>49.0504150390625</v>
-      </c>
-      <c r="E72">
-        <f>A72-C72</f>
-        <v>0.40310668945320316</v>
-      </c>
-      <c r="F72">
-        <f>B72-D72</f>
-        <v>-1.0504150390625</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73">
-        <v>48</v>
-      </c>
-      <c r="B73">
-        <v>842</v>
-      </c>
-      <c r="C73">
-        <v>45.755180358886697</v>
-      </c>
-      <c r="D73">
-        <v>841.51623535156205</v>
-      </c>
-      <c r="E73">
-        <f>A73-C73</f>
-        <v>2.2448196411133026</v>
-      </c>
-      <c r="F73">
-        <f>B73-D73</f>
-        <v>0.48376464843795475</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74">
-        <v>48</v>
-      </c>
-      <c r="B74">
-        <v>842</v>
-      </c>
-      <c r="C74">
-        <v>46.4288520812988</v>
-      </c>
-      <c r="D74">
-        <v>841.85144042968705</v>
-      </c>
-      <c r="E74">
-        <f>A74-C74</f>
-        <v>1.5711479187012003</v>
-      </c>
-      <c r="F74">
-        <f>B74-D74</f>
-        <v>0.14855957031295475</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75">
-        <v>48</v>
-      </c>
-      <c r="B75">
-        <v>842</v>
-      </c>
-      <c r="C75">
-        <v>45.449230194091797</v>
-      </c>
-      <c r="D75">
-        <v>841.79510498046795</v>
-      </c>
-      <c r="E75">
-        <f>A75-C75</f>
-        <v>2.5507698059082031</v>
-      </c>
-      <c r="F75">
-        <f>B75-D75</f>
-        <v>0.20489501953204581</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76">
-        <v>48</v>
-      </c>
-      <c r="B76">
-        <v>842</v>
-      </c>
-      <c r="C76">
-        <v>45.761184692382798</v>
-      </c>
-      <c r="D76">
-        <v>841.80145263671795</v>
-      </c>
-      <c r="E76">
-        <f>A76-C76</f>
-        <v>2.2388153076172017</v>
-      </c>
-      <c r="F76">
-        <f>B76-D76</f>
-        <v>0.19854736328204581</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77">
-        <v>48</v>
-      </c>
-      <c r="B77">
-        <v>842</v>
-      </c>
-      <c r="C77">
-        <v>46.424354553222599</v>
-      </c>
-      <c r="D77">
-        <v>841.849853515625</v>
-      </c>
-      <c r="E77">
-        <f>A77-C77</f>
-        <v>1.5756454467774006</v>
-      </c>
-      <c r="F77">
-        <f>B77-D77</f>
-        <v>0.150146484375</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78">
-        <v>48</v>
-      </c>
-      <c r="B78">
-        <v>842</v>
-      </c>
-      <c r="C78">
-        <v>46.676059722900298</v>
-      </c>
-      <c r="D78">
-        <v>841.57489013671795</v>
-      </c>
-      <c r="E78">
-        <f>A78-C78</f>
-        <v>1.3239402770997017</v>
-      </c>
-      <c r="F78">
-        <f>B78-D78</f>
-        <v>0.42510986328204581</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79">
-        <v>48</v>
-      </c>
-      <c r="B79">
-        <v>842</v>
-      </c>
-      <c r="C79">
-        <v>46.1204223632812</v>
-      </c>
-      <c r="D79">
-        <v>842.09362792968705</v>
-      </c>
-      <c r="E79">
-        <f>A79-C79</f>
-        <v>1.8795776367187997</v>
-      </c>
-      <c r="F79">
-        <f>B79-D79</f>
-        <v>-9.3627929687045253E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80">
-        <v>48</v>
-      </c>
-      <c r="B80">
-        <v>842</v>
-      </c>
-      <c r="C80">
-        <v>45.755908966064403</v>
-      </c>
-      <c r="D80">
-        <v>841.80029296875</v>
-      </c>
-      <c r="E80">
-        <f>A80-C80</f>
-        <v>2.2440910339355966</v>
-      </c>
-      <c r="F80">
-        <f>B80-D80</f>
-        <v>0.19970703125</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81">
-        <v>48</v>
-      </c>
-      <c r="B81">
-        <v>842</v>
-      </c>
-      <c r="C81">
-        <v>45.559959411621001</v>
-      </c>
-      <c r="D81">
-        <v>841.79577636718705</v>
-      </c>
-      <c r="E81">
-        <f>A81-C81</f>
-        <v>2.4400405883789986</v>
-      </c>
-      <c r="F81">
-        <f>B81-D81</f>
-        <v>0.20422363281295475</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82">
-        <v>48</v>
-      </c>
-      <c r="B82">
-        <v>842</v>
-      </c>
-      <c r="C82">
-        <v>46.622611999511697</v>
-      </c>
-      <c r="D82">
-        <v>842.06854248046795</v>
-      </c>
-      <c r="E82">
-        <f>A82-C82</f>
-        <v>1.3773880004883026</v>
-      </c>
-      <c r="F82">
-        <f>B82-D82</f>
-        <v>-6.8542480467954192E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83">
-        <v>48</v>
-      </c>
-      <c r="B83">
-        <v>842</v>
-      </c>
-      <c r="C83">
-        <v>46.258689880371001</v>
-      </c>
-      <c r="D83">
-        <v>841.98822021484295</v>
-      </c>
-      <c r="E83">
-        <f>A83-C83</f>
-        <v>1.7413101196289986</v>
-      </c>
-      <c r="F83">
-        <f>B83-D83</f>
-        <v>1.1779785157045808E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84">
-        <v>48</v>
-      </c>
-      <c r="B84">
-        <v>842</v>
-      </c>
-      <c r="C84">
-        <v>46.320598602294901</v>
-      </c>
-      <c r="D84">
-        <v>841.88726806640602</v>
-      </c>
-      <c r="E84">
-        <f>A84-C84</f>
-        <v>1.6794013977050994</v>
-      </c>
-      <c r="F84">
-        <f>B84-D84</f>
-        <v>0.11273193359397737</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85">
-        <v>48</v>
-      </c>
-      <c r="B85">
-        <v>842</v>
-      </c>
-      <c r="C85">
-        <v>46.427742004394503</v>
-      </c>
-      <c r="D85">
-        <v>841.886474609375</v>
-      </c>
-      <c r="E85">
-        <f>A85-C85</f>
-        <v>1.5722579956054972</v>
-      </c>
-      <c r="F85">
-        <f>B85-D85</f>
-        <v>0.113525390625</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86">
-        <v>48</v>
-      </c>
-      <c r="B86">
-        <v>842</v>
-      </c>
-      <c r="C86">
-        <v>46.374229431152301</v>
-      </c>
-      <c r="D86">
-        <v>841.88671875</v>
-      </c>
-      <c r="E86">
-        <f>A86-C86</f>
-        <v>1.6257705688476989</v>
-      </c>
-      <c r="F86">
-        <f>B86-D86</f>
-        <v>0.11328125</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87">
-        <v>48</v>
-      </c>
-      <c r="B87">
-        <v>842</v>
-      </c>
-      <c r="C87">
-        <v>46.370735168457003</v>
-      </c>
-      <c r="D87">
-        <v>841.850341796875</v>
-      </c>
-      <c r="E87">
-        <f>A87-C87</f>
-        <v>1.6292648315429972</v>
-      </c>
-      <c r="F87">
-        <f>B87-D87</f>
-        <v>0.149658203125</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88">
-        <v>48</v>
-      </c>
-      <c r="B88">
-        <v>842</v>
-      </c>
-      <c r="C88">
-        <v>45.70308303833</v>
-      </c>
-      <c r="D88">
-        <v>841.80090332031205</v>
-      </c>
-      <c r="E88">
-        <f>A88-C88</f>
-        <v>2.29691696167</v>
-      </c>
-      <c r="F88">
-        <f>B88-D88</f>
-        <v>0.19909667968795475</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89">
-        <v>48</v>
-      </c>
-      <c r="B89">
-        <v>842</v>
-      </c>
-      <c r="C89">
-        <v>46.317268371582003</v>
-      </c>
-      <c r="D89">
-        <v>841.8505859375</v>
-      </c>
-      <c r="E89">
-        <f>A89-C89</f>
-        <v>1.6827316284179972</v>
-      </c>
-      <c r="F89">
-        <f>B89-D89</f>
-        <v>0.1494140625</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90">
-        <v>48</v>
-      </c>
-      <c r="B90">
-        <v>842</v>
-      </c>
-      <c r="C90">
-        <v>45.556205749511697</v>
-      </c>
-      <c r="D90">
-        <v>841.70202636718705</v>
-      </c>
-      <c r="E90">
-        <f>A90-C90</f>
-        <v>2.4437942504883026</v>
-      </c>
-      <c r="F90">
-        <f>B90-D90</f>
-        <v>0.29797363281295475</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91">
-        <v>48</v>
-      </c>
-      <c r="B91">
-        <v>842</v>
-      </c>
-      <c r="C91">
-        <v>45.70308303833</v>
-      </c>
-      <c r="D91">
-        <v>841.80090332031205</v>
-      </c>
-      <c r="E91">
-        <f>A91-C91</f>
-        <v>2.29691696167</v>
-      </c>
-      <c r="F91">
-        <f>B91-D91</f>
-        <v>0.19909667968795475</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92">
-        <v>48</v>
-      </c>
-      <c r="B92">
-        <v>842</v>
-      </c>
-      <c r="C92">
-        <v>45.653617858886697</v>
-      </c>
-      <c r="D92">
-        <v>841.83734130859295</v>
-      </c>
-      <c r="E92">
-        <f>A92-C92</f>
-        <v>2.3463821411133026</v>
-      </c>
-      <c r="F92">
-        <f>B92-D92</f>
-        <v>0.16265869140704581</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93">
-        <v>48</v>
-      </c>
-      <c r="B93">
-        <v>842</v>
-      </c>
-      <c r="C93">
-        <v>46.320598602294901</v>
-      </c>
-      <c r="D93">
-        <v>841.88726806640602</v>
-      </c>
-      <c r="E93">
-        <f>A93-C93</f>
-        <v>1.6794013977050994</v>
-      </c>
-      <c r="F93">
-        <f>B93-D93</f>
-        <v>0.11273193359397737</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94">
-        <v>48</v>
-      </c>
-      <c r="B94">
-        <v>842</v>
-      </c>
-      <c r="C94">
-        <v>45.814079284667898</v>
-      </c>
-      <c r="D94">
-        <v>841.80163574218705</v>
-      </c>
-      <c r="E94">
-        <f>A94-C94</f>
-        <v>2.1859207153321023</v>
-      </c>
-      <c r="F94">
-        <f>B94-D94</f>
-        <v>0.19836425781295475</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95">
-        <v>48</v>
-      </c>
-      <c r="B95">
-        <v>842</v>
-      </c>
-      <c r="C95">
-        <v>46.370735168457003</v>
-      </c>
-      <c r="D95">
-        <v>841.850341796875</v>
-      </c>
-      <c r="E95">
-        <f>A95-C95</f>
-        <v>1.6292648315429972</v>
-      </c>
-      <c r="F95">
-        <f>B95-D95</f>
-        <v>0.149658203125</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96">
-        <v>48</v>
-      </c>
-      <c r="B96">
-        <v>842</v>
-      </c>
-      <c r="C96">
-        <v>45.656631469726499</v>
-      </c>
-      <c r="D96">
-        <v>842.08642578125</v>
-      </c>
-      <c r="E96">
-        <f>A96-C96</f>
-        <v>2.3433685302735014</v>
-      </c>
-      <c r="F96">
-        <f>B96-D96</f>
-        <v>-8.642578125E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97">
-        <v>48</v>
-      </c>
-      <c r="B97">
-        <v>842</v>
-      </c>
-      <c r="C97">
-        <v>46.171791076660099</v>
-      </c>
-      <c r="D97">
-        <v>841.809326171875</v>
-      </c>
-      <c r="E97">
-        <f>A97-C97</f>
-        <v>1.8282089233399006</v>
-      </c>
-      <c r="F97">
-        <f>B97-D97</f>
-        <v>0.190673828125</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98">
-        <v>48</v>
-      </c>
-      <c r="B98">
-        <v>842</v>
-      </c>
-      <c r="C98">
-        <v>45.752861022949197</v>
-      </c>
-      <c r="D98">
-        <v>841.55432128906205</v>
-      </c>
-      <c r="E98">
-        <f>A98-C98</f>
-        <v>2.2471389770508026</v>
-      </c>
-      <c r="F98">
-        <f>B98-D98</f>
-        <v>0.44567871093795475</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99">
-        <v>48</v>
-      </c>
-      <c r="B99">
-        <v>842</v>
-      </c>
-      <c r="C99">
-        <v>46.421051025390597</v>
-      </c>
-      <c r="D99">
-        <v>841.60076904296795</v>
-      </c>
-      <c r="E99">
-        <f>A99-C99</f>
-        <v>1.5789489746094034</v>
-      </c>
-      <c r="F99">
-        <f>B99-D99</f>
-        <v>0.39923095703204581</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100">
-        <v>48</v>
-      </c>
-      <c r="B100">
-        <v>842</v>
-      </c>
-      <c r="C100">
-        <v>45.706104278564403</v>
-      </c>
-      <c r="D100">
-        <v>842.050048828125</v>
-      </c>
-      <c r="E100">
-        <f>A100-C100</f>
-        <v>2.2938957214355966</v>
-      </c>
-      <c r="F100">
-        <f>B100-D100</f>
-        <v>-5.0048828125E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101">
-        <v>48</v>
-      </c>
-      <c r="B101">
-        <v>842</v>
-      </c>
-      <c r="C101">
-        <v>46.427658081054602</v>
-      </c>
-      <c r="D101">
-        <v>842.09881591796795</v>
-      </c>
-      <c r="E101">
-        <f>A101-C101</f>
-        <v>1.5723419189453978</v>
-      </c>
-      <c r="F101">
-        <f>B101-D101</f>
-        <v>-9.8815917967954192E-2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102">
-        <v>48</v>
-      </c>
-      <c r="B102">
-        <v>842</v>
-      </c>
-      <c r="C102">
-        <v>45.904170989990199</v>
-      </c>
-      <c r="D102">
-        <v>841.59735107421795</v>
-      </c>
-      <c r="E102">
-        <f>A102-C102</f>
-        <v>2.0958290100098012</v>
-      </c>
-      <c r="F102">
-        <f>B102-D102</f>
-        <v>0.40264892578204581</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103">
-        <v>48</v>
-      </c>
-      <c r="B103">
-        <v>842</v>
-      </c>
-      <c r="C103">
-        <v>45.70308303833</v>
-      </c>
-      <c r="D103">
-        <v>841.80090332031205</v>
-      </c>
-      <c r="E103">
-        <f>A103-C103</f>
-        <v>2.29691696167</v>
-      </c>
-      <c r="F103">
-        <f>B103-D103</f>
-        <v>0.19909667968795475</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104">
-        <v>48</v>
-      </c>
-      <c r="B104">
-        <v>842</v>
-      </c>
-      <c r="C104">
-        <v>46.374034881591797</v>
-      </c>
-      <c r="D104">
-        <v>842.099365234375</v>
-      </c>
-      <c r="E104">
-        <f>A104-C104</f>
-        <v>1.6259651184082031</v>
-      </c>
-      <c r="F104">
-        <f>B104-D104</f>
-        <v>-9.9365234375E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105">
-        <v>48</v>
-      </c>
-      <c r="B105">
-        <v>842</v>
-      </c>
-      <c r="C105">
-        <v>45.759239196777301</v>
-      </c>
-      <c r="D105">
-        <v>841.8369140625</v>
-      </c>
-      <c r="E105">
-        <f>A105-C105</f>
-        <v>2.2407608032226989</v>
-      </c>
-      <c r="F105">
-        <f>B105-D105</f>
-        <v>0.1630859375</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106">
-        <v>48</v>
-      </c>
-      <c r="B106">
-        <v>842</v>
-      </c>
-      <c r="C106">
-        <v>46.479072570800703</v>
-      </c>
-      <c r="D106">
-        <v>841.81451416015602</v>
-      </c>
-      <c r="E106">
-        <f>A106-C106</f>
-        <v>1.5209274291992969</v>
-      </c>
-      <c r="F106">
-        <f>B106-D106</f>
-        <v>0.18548583984397737</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107">
-        <v>48</v>
-      </c>
-      <c r="B107">
-        <v>842</v>
-      </c>
-      <c r="C107">
-        <v>45.704360961913999</v>
-      </c>
-      <c r="D107">
-        <v>842.04998779296795</v>
-      </c>
-      <c r="E107">
-        <f>A107-C107</f>
-        <v>2.2956390380860014</v>
-      </c>
-      <c r="F107">
-        <f>B107-D107</f>
-        <v>-4.9987792967954192E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108">
-        <v>48</v>
-      </c>
-      <c r="B108">
-        <v>842</v>
-      </c>
-      <c r="C108">
-        <v>45.924018859863203</v>
-      </c>
-      <c r="D108">
-        <v>842.03192138671795</v>
-      </c>
-      <c r="E108">
-        <f>A108-C108</f>
-        <v>2.0759811401367969</v>
-      </c>
-      <c r="F108">
-        <f>B108-D108</f>
-        <v>-3.1921386717954192E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109">
-        <v>48</v>
-      </c>
-      <c r="B109">
-        <v>842</v>
-      </c>
-      <c r="C109">
-        <v>46.367431640625</v>
-      </c>
-      <c r="D109">
-        <v>841.601318359375</v>
-      </c>
-      <c r="E109">
-        <f>A109-C109</f>
-        <v>1.632568359375</v>
-      </c>
-      <c r="F109">
-        <f>B109-D109</f>
-        <v>0.398681640625</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110">
-        <v>48</v>
-      </c>
-      <c r="B110">
-        <v>842</v>
-      </c>
-      <c r="C110">
-        <v>45.454765319824197</v>
-      </c>
-      <c r="D110">
-        <v>841.796142578125</v>
-      </c>
-      <c r="E110">
-        <f>A110-C110</f>
-        <v>2.5452346801758026</v>
-      </c>
-      <c r="F110">
-        <f>B110-D110</f>
-        <v>0.203857421875</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111">
-        <v>48</v>
-      </c>
-      <c r="B111">
-        <v>842</v>
-      </c>
-      <c r="C111">
-        <v>46.370735168457003</v>
-      </c>
-      <c r="D111">
-        <v>841.850341796875</v>
-      </c>
-      <c r="E111">
-        <f>A111-C111</f>
-        <v>1.6292648315429972</v>
-      </c>
-      <c r="F111">
-        <f>B111-D111</f>
-        <v>0.149658203125</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112">
-        <v>48</v>
-      </c>
-      <c r="B112">
-        <v>842</v>
-      </c>
-      <c r="C112">
-        <v>46.427742004394503</v>
-      </c>
-      <c r="D112">
-        <v>841.886474609375</v>
-      </c>
-      <c r="E112">
-        <f>A112-C112</f>
-        <v>1.5722579956054972</v>
-      </c>
-      <c r="F112">
-        <f>B112-D112</f>
-        <v>0.113525390625</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113">
-        <v>48</v>
-      </c>
-      <c r="B113">
-        <v>842</v>
-      </c>
-      <c r="C113">
-        <v>46.320598602294901</v>
-      </c>
-      <c r="D113">
-        <v>841.88726806640602</v>
-      </c>
-      <c r="E113">
-        <f>A113-C113</f>
-        <v>1.6794013977050994</v>
-      </c>
-      <c r="F113">
-        <f>B113-D113</f>
-        <v>0.11273193359397737</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114">
-        <v>48</v>
-      </c>
-      <c r="B114">
-        <v>842</v>
-      </c>
-      <c r="C114">
-        <v>46.370735168457003</v>
-      </c>
-      <c r="D114">
-        <v>841.850341796875</v>
-      </c>
-      <c r="E114">
-        <f>A114-C114</f>
-        <v>1.6292648315429972</v>
-      </c>
-      <c r="F114">
-        <f>B114-D114</f>
-        <v>0.149658203125</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115">
-        <v>48</v>
-      </c>
-      <c r="B115">
-        <v>842</v>
-      </c>
-      <c r="C115">
-        <v>45.757900238037102</v>
-      </c>
-      <c r="D115">
-        <v>841.76550292968705</v>
-      </c>
-      <c r="E115">
-        <f>A115-C115</f>
-        <v>2.2420997619628977</v>
-      </c>
-      <c r="F115">
-        <f>B115-D115</f>
-        <v>0.23449707031295475</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116">
-        <v>48</v>
-      </c>
-      <c r="B116">
-        <v>842</v>
-      </c>
-      <c r="C116">
-        <v>46.120529174804602</v>
-      </c>
-      <c r="D116">
-        <v>841.88073730468705</v>
-      </c>
-      <c r="E116">
-        <f>A116-C116</f>
-        <v>1.8794708251953978</v>
-      </c>
-      <c r="F116">
-        <f>B116-D116</f>
-        <v>0.11926269531295475</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117">
-        <v>48</v>
-      </c>
-      <c r="B117">
-        <v>842</v>
-      </c>
-      <c r="C117">
-        <v>45.958572387695298</v>
-      </c>
-      <c r="D117">
-        <v>841.84259033203102</v>
-      </c>
-      <c r="E117">
-        <f>A117-C117</f>
-        <v>2.0414276123047017</v>
-      </c>
-      <c r="F117">
-        <f>B117-D117</f>
-        <v>0.15740966796897737</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118">
-        <v>48</v>
-      </c>
-      <c r="B118">
-        <v>842</v>
-      </c>
-      <c r="C118">
-        <v>45.706447601318303</v>
-      </c>
-      <c r="D118">
-        <v>841.836669921875</v>
-      </c>
-      <c r="E118">
-        <f>A118-C118</f>
-        <v>2.2935523986816975</v>
-      </c>
-      <c r="F118">
-        <f>B118-D118</f>
-        <v>0.163330078125</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119">
-        <v>48</v>
-      </c>
-      <c r="B119">
-        <v>842</v>
-      </c>
-      <c r="C119">
-        <v>46.674980163574197</v>
-      </c>
-      <c r="D119">
-        <v>841.60986328125</v>
-      </c>
-      <c r="E119">
-        <f>A119-C119</f>
-        <v>1.3250198364258026</v>
-      </c>
-      <c r="F119">
-        <f>B119-D119</f>
-        <v>0.39013671875</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120">
-        <v>48</v>
-      </c>
-      <c r="B120">
-        <v>842</v>
-      </c>
-      <c r="C120">
-        <v>46.375831604003899</v>
-      </c>
-      <c r="D120">
-        <v>842.13580322265602</v>
-      </c>
-      <c r="E120">
-        <f>A120-C120</f>
-        <v>1.6241683959961009</v>
-      </c>
-      <c r="F120">
-        <f>B120-D120</f>
-        <v>-0.13580322265602263</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121">
-        <v>48</v>
-      </c>
-      <c r="B121">
-        <v>842</v>
-      </c>
-      <c r="C121">
-        <v>45.866954803466797</v>
-      </c>
-      <c r="D121">
-        <v>841.80096435546795</v>
-      </c>
-      <c r="E121">
-        <f>A121-C121</f>
-        <v>2.1330451965332031</v>
-      </c>
-      <c r="F121">
-        <f>B121-D121</f>
-        <v>0.19903564453204581</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122">
-        <v>48</v>
-      </c>
-      <c r="B122">
-        <v>842</v>
-      </c>
-      <c r="C122">
-        <v>46.323898315429602</v>
-      </c>
-      <c r="D122">
-        <v>842.13623046875</v>
-      </c>
-      <c r="E122">
-        <f>A122-C122</f>
-        <v>1.6761016845703978</v>
-      </c>
-      <c r="F122">
-        <f>B122-D122</f>
-        <v>-0.13623046875</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123">
-        <v>48</v>
-      </c>
-      <c r="B123">
-        <v>842</v>
-      </c>
-      <c r="C123">
-        <v>46.375205993652301</v>
-      </c>
-      <c r="D123">
-        <v>841.85205078125</v>
-      </c>
-      <c r="E123">
-        <f>A123-C123</f>
-        <v>1.6247940063476989</v>
-      </c>
-      <c r="F123">
-        <f>B123-D123</f>
-        <v>0.14794921875</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124">
-        <v>48</v>
-      </c>
-      <c r="B124">
-        <v>842</v>
-      </c>
-      <c r="C124">
-        <v>46.427742004394503</v>
-      </c>
-      <c r="D124">
-        <v>841.886474609375</v>
-      </c>
-      <c r="E124">
-        <f>A124-C124</f>
-        <v>1.5722579956054972</v>
-      </c>
-      <c r="F124">
-        <f>B124-D124</f>
-        <v>0.113525390625</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125">
-        <v>48</v>
-      </c>
-      <c r="B125">
-        <v>842</v>
-      </c>
-      <c r="C125">
-        <v>46.482463836669901</v>
-      </c>
-      <c r="D125">
-        <v>841.85113525390602</v>
-      </c>
-      <c r="E125">
-        <f>A125-C125</f>
-        <v>1.5175361633300994</v>
-      </c>
-      <c r="F125">
-        <f>B125-D125</f>
-        <v>0.14886474609397737</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126">
-        <v>48</v>
-      </c>
-      <c r="B126">
-        <v>842</v>
-      </c>
-      <c r="C126">
-        <v>45.706447601318303</v>
-      </c>
-      <c r="D126">
-        <v>841.836669921875</v>
-      </c>
-      <c r="E126">
-        <f>A126-C126</f>
-        <v>2.2935523986816975</v>
-      </c>
-      <c r="F126">
-        <f>B126-D126</f>
-        <v>0.163330078125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127">
-        <v>48</v>
-      </c>
-      <c r="B127">
-        <v>842</v>
-      </c>
-      <c r="C127">
-        <v>46.432235717773402</v>
-      </c>
-      <c r="D127">
-        <v>841.88806152343705</v>
-      </c>
-      <c r="E127">
-        <f>A127-C127</f>
-        <v>1.567764282226598</v>
-      </c>
-      <c r="F127">
-        <f>B127-D127</f>
-        <v>0.11193847656295475</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128">
-        <v>48</v>
-      </c>
-      <c r="B128">
-        <v>842</v>
-      </c>
-      <c r="C128">
-        <v>46.170402526855398</v>
-      </c>
-      <c r="D128">
-        <v>841.84405517578102</v>
-      </c>
-      <c r="E128">
-        <f>A128-C128</f>
-        <v>1.8295974731446023</v>
-      </c>
-      <c r="F128">
-        <f>B128-D128</f>
-        <v>0.15594482421897737</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129">
-        <v>48</v>
-      </c>
-      <c r="B129">
-        <v>842</v>
-      </c>
-      <c r="C129">
-        <v>45.973758697509702</v>
-      </c>
-      <c r="D129">
-        <v>841.99530029296795</v>
-      </c>
-      <c r="E129">
-        <f>A129-C129</f>
-        <v>2.0262413024902983</v>
-      </c>
-      <c r="F129">
-        <f>B129-D129</f>
-        <v>4.6997070320458079E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130">
-        <v>48</v>
-      </c>
-      <c r="B130">
-        <v>842</v>
-      </c>
-      <c r="C130">
-        <v>46.4288520812988</v>
-      </c>
-      <c r="D130">
-        <v>841.85144042968705</v>
-      </c>
-      <c r="E130">
-        <f>A130-C130</f>
-        <v>1.5711479187012003</v>
-      </c>
-      <c r="F130">
-        <f>B130-D130</f>
-        <v>0.14855957031295475</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131">
-        <v>48</v>
-      </c>
-      <c r="B131">
-        <v>842</v>
-      </c>
-      <c r="C131">
-        <v>45.559474945068303</v>
-      </c>
-      <c r="D131">
-        <v>841.73767089843705</v>
-      </c>
-      <c r="E131">
-        <f>A131-C131</f>
-        <v>2.4405250549316975</v>
-      </c>
-      <c r="F131">
-        <f>B131-D131</f>
-        <v>0.26232910156295475</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132">
-        <v>48</v>
-      </c>
-      <c r="B132">
-        <v>842</v>
-      </c>
-      <c r="C132">
-        <v>45.814079284667898</v>
-      </c>
-      <c r="D132">
-        <v>841.80163574218705</v>
-      </c>
-      <c r="E132">
-        <f>A132-C132</f>
-        <v>2.1859207153321023</v>
-      </c>
-      <c r="F132">
-        <f>B132-D132</f>
-        <v>0.19836425781295475</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133">
-        <v>48</v>
-      </c>
-      <c r="B133">
-        <v>842</v>
-      </c>
-      <c r="C133">
-        <v>46.320598602294901</v>
-      </c>
-      <c r="D133">
-        <v>841.88726806640602</v>
-      </c>
-      <c r="E133">
-        <f>A133-C133</f>
-        <v>1.6794013977050994</v>
-      </c>
-      <c r="F133">
-        <f>B133-D133</f>
-        <v>0.11273193359397737</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134">
-        <v>48</v>
-      </c>
-      <c r="B134">
-        <v>842</v>
-      </c>
-      <c r="C134">
-        <v>45.70308303833</v>
-      </c>
-      <c r="D134">
-        <v>841.80090332031205</v>
-      </c>
-      <c r="E134">
-        <f>A134-C134</f>
-        <v>2.29691696167</v>
-      </c>
-      <c r="F134">
-        <f>B134-D134</f>
-        <v>0.19909667968795475</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135">
-        <v>48</v>
-      </c>
-      <c r="B135">
-        <v>842</v>
-      </c>
-      <c r="C135">
-        <v>45.902870178222599</v>
-      </c>
-      <c r="D135">
-        <v>841.35144042968705</v>
-      </c>
-      <c r="E135">
-        <f>A135-C135</f>
-        <v>2.0971298217774006</v>
-      </c>
-      <c r="F135">
-        <f>B135-D135</f>
-        <v>0.64855957031295475</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136">
-        <v>48</v>
-      </c>
-      <c r="B136">
-        <v>842</v>
-      </c>
-      <c r="C136">
-        <v>46.425437927246001</v>
-      </c>
-      <c r="D136">
-        <v>841.81506347656205</v>
-      </c>
-      <c r="E136">
-        <f>A136-C136</f>
-        <v>1.5745620727539986</v>
-      </c>
-      <c r="F136">
-        <f>B136-D136</f>
-        <v>0.18493652343795475</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137">
-        <v>48</v>
-      </c>
-      <c r="B137">
-        <v>842</v>
-      </c>
-      <c r="C137">
-        <v>45.817150115966797</v>
-      </c>
-      <c r="D137">
-        <v>842.12438964843705</v>
-      </c>
-      <c r="E137">
-        <f>A137-C137</f>
-        <v>2.1828498840332031</v>
-      </c>
-      <c r="F137">
-        <f>B137-D137</f>
-        <v>-0.12438964843704525</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138">
-        <v>48</v>
-      </c>
-      <c r="B138">
-        <v>842</v>
-      </c>
-      <c r="C138">
-        <v>46.454917907714801</v>
-      </c>
-      <c r="D138">
-        <v>841.77984619140602</v>
-      </c>
-      <c r="E138">
-        <f>A138-C138</f>
-        <v>1.5450820922851989</v>
-      </c>
-      <c r="F138">
-        <f>B138-D138</f>
-        <v>0.22015380859397737</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139">
-        <v>48</v>
-      </c>
-      <c r="B139">
-        <v>842</v>
-      </c>
-      <c r="C139">
-        <v>45.870510101318303</v>
-      </c>
-      <c r="D139">
-        <v>841.63116455078102</v>
-      </c>
-      <c r="E139">
-        <f>A139-C139</f>
-        <v>2.1294898986816975</v>
-      </c>
-      <c r="F139">
-        <f>B139-D139</f>
-        <v>0.36883544921897737</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140">
-        <v>48</v>
-      </c>
-      <c r="B140">
-        <v>842</v>
-      </c>
-      <c r="C140">
-        <v>46.370735168457003</v>
-      </c>
-      <c r="D140">
-        <v>841.850341796875</v>
-      </c>
-      <c r="E140">
-        <f>A140-C140</f>
-        <v>1.6292648315429972</v>
-      </c>
-      <c r="F140">
-        <f>B140-D140</f>
-        <v>0.149658203125</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141">
-        <v>48</v>
-      </c>
-      <c r="B141">
-        <v>842</v>
-      </c>
-      <c r="C141">
-        <v>46.433540344238203</v>
-      </c>
-      <c r="D141">
-        <v>842.13702392578102</v>
-      </c>
-      <c r="E141">
-        <f>A141-C141</f>
-        <v>1.5664596557617969</v>
-      </c>
-      <c r="F141">
-        <f>B141-D141</f>
-        <v>-0.13702392578102263</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142">
-        <v>48</v>
-      </c>
-      <c r="B142">
-        <v>842</v>
-      </c>
-      <c r="C142">
-        <v>46.4282836914062</v>
-      </c>
-      <c r="D142">
-        <v>841.79437255859295</v>
-      </c>
-      <c r="E142">
-        <f>A142-C142</f>
-        <v>1.5717163085937997</v>
-      </c>
-      <c r="F142">
-        <f>B142-D142</f>
-        <v>0.20562744140704581</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143">
-        <v>48</v>
-      </c>
-      <c r="B143">
-        <v>842</v>
-      </c>
-      <c r="C143">
-        <v>45.694984436035099</v>
-      </c>
-      <c r="D143">
-        <v>841.66796875</v>
-      </c>
-      <c r="E143">
-        <f>A143-C143</f>
-        <v>2.3050155639649006</v>
-      </c>
-      <c r="F143">
-        <f>B143-D143</f>
-        <v>0.33203125</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B144">
-        <v>48</v>
-      </c>
-      <c r="C144">
-        <v>1213.24365234375</v>
-      </c>
-      <c r="D144">
-        <v>48.741989135742102</v>
-      </c>
-      <c r="E144">
-        <f>A144-C144</f>
-        <v>-1.24365234375</v>
-      </c>
-      <c r="F144">
-        <f>B144-D144</f>
-        <v>-0.74198913574210223</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B145">
-        <v>48</v>
-      </c>
-      <c r="C145">
-        <v>1213.53063964843</v>
-      </c>
-      <c r="D145">
-        <v>48.473655700683501</v>
-      </c>
-      <c r="E145">
-        <f>A145-C145</f>
-        <v>-1.5306396484299967</v>
-      </c>
-      <c r="F145">
-        <f>B145-D145</f>
-        <v>-0.47365570068350138</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B146">
-        <v>48</v>
-      </c>
-      <c r="C146">
-        <v>1212.57385253906</v>
-      </c>
-      <c r="D146">
-        <v>48.134490966796797</v>
-      </c>
-      <c r="E146">
-        <f>A146-C146</f>
-        <v>-0.57385253905999889</v>
-      </c>
-      <c r="F146">
-        <f>B146-D146</f>
-        <v>-0.13449096679679684</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B147">
-        <v>48</v>
-      </c>
-      <c r="C147">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D147">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E147">
-        <f>A147-C147</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F147">
-        <f>B147-D147</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A148">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B148">
-        <v>48</v>
-      </c>
-      <c r="C148">
-        <v>1213.53063964843</v>
-      </c>
-      <c r="D148">
-        <v>48.473655700683501</v>
-      </c>
-      <c r="E148">
-        <f>A148-C148</f>
-        <v>-1.5306396484299967</v>
-      </c>
-      <c r="F148">
-        <f>B148-D148</f>
-        <v>-0.47365570068350138</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A149">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B149">
-        <v>48</v>
-      </c>
-      <c r="C149">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D149">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E149">
-        <f>A149-C149</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F149">
-        <f>B149-D149</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A150">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B150">
-        <v>48</v>
-      </c>
-      <c r="C150">
-        <v>1213.28015136718</v>
-      </c>
-      <c r="D150">
-        <v>48.154129028320298</v>
-      </c>
-      <c r="E150">
-        <f>A150-C150</f>
-        <v>-1.2801513671799967</v>
-      </c>
-      <c r="F150">
-        <f>B150-D150</f>
-        <v>-0.15412902832029829</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A151">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B151">
-        <v>48</v>
-      </c>
-      <c r="C151">
-        <v>1213.09985351562</v>
-      </c>
-      <c r="D151">
-        <v>48.3029174804687</v>
-      </c>
-      <c r="E151">
-        <f>A151-C151</f>
-        <v>-1.0998535156199978</v>
-      </c>
-      <c r="F151">
-        <f>B151-D151</f>
-        <v>-0.30291748046870026</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B152">
-        <v>48</v>
-      </c>
-      <c r="C152">
-        <v>1213.54968261718</v>
-      </c>
-      <c r="D152">
-        <v>48.195144653320298</v>
-      </c>
-      <c r="E152">
-        <f>A152-C152</f>
-        <v>-1.5496826171799967</v>
-      </c>
-      <c r="F152">
-        <f>B152-D152</f>
-        <v>-0.19514465332029829</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B153">
-        <v>48</v>
-      </c>
-      <c r="C153">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D153">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E153">
-        <f>A153-C153</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F153">
-        <f>B153-D153</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A154">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B154">
-        <v>48</v>
-      </c>
-      <c r="C154">
-        <v>1213.16064453125</v>
-      </c>
-      <c r="D154">
-        <v>48.554695129394503</v>
-      </c>
-      <c r="E154">
-        <f>A154-C154</f>
-        <v>-1.16064453125</v>
-      </c>
-      <c r="F154">
-        <f>B154-D154</f>
-        <v>-0.55469512939450283</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A155">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B155">
-        <v>48</v>
-      </c>
-      <c r="C155">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D155">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E155">
-        <f>A155-C155</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F155">
-        <f>B155-D155</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B156">
-        <v>48</v>
-      </c>
-      <c r="C156">
-        <v>1213.28344726562</v>
-      </c>
-      <c r="D156">
-        <v>48.188583374023402</v>
-      </c>
-      <c r="E156">
-        <f>A156-C156</f>
-        <v>-1.2834472656199978</v>
-      </c>
-      <c r="F156">
-        <f>B156-D156</f>
-        <v>-0.18858337402340197</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A157">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B157">
-        <v>48</v>
-      </c>
-      <c r="C157">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D157">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E157">
-        <f>A157-C157</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F157">
-        <f>B157-D157</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B158">
-        <v>48</v>
-      </c>
-      <c r="C158">
-        <v>1213.03588867187</v>
-      </c>
-      <c r="D158">
-        <v>48.388885498046797</v>
-      </c>
-      <c r="E158">
-        <f>A158-C158</f>
-        <v>-1.0358886718699978</v>
-      </c>
-      <c r="F158">
-        <f>B158-D158</f>
-        <v>-0.38888549804679684</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A159">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B159">
-        <v>48</v>
-      </c>
-      <c r="C159">
-        <v>1213.21240234375</v>
-      </c>
-      <c r="D159">
-        <v>48.521339416503899</v>
-      </c>
-      <c r="E159">
-        <f>A159-C159</f>
-        <v>-1.21240234375</v>
-      </c>
-      <c r="F159">
-        <f>B159-D159</f>
-        <v>-0.52133941650389914</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B160">
-        <v>48</v>
-      </c>
-      <c r="C160">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D160">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E160">
-        <f>A160-C160</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F160">
-        <f>B160-D160</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B161">
-        <v>48</v>
-      </c>
-      <c r="C161">
-        <v>1213.12194824218</v>
-      </c>
-      <c r="D161">
-        <v>48.062187194824197</v>
-      </c>
-      <c r="E161">
-        <f>A161-C161</f>
-        <v>-1.1219482421799967</v>
-      </c>
-      <c r="F161">
-        <f>B161-D161</f>
-        <v>-6.2187194824197434E-2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B162">
-        <v>48</v>
-      </c>
-      <c r="C162">
-        <v>1213.28344726562</v>
-      </c>
-      <c r="D162">
-        <v>48.188583374023402</v>
-      </c>
-      <c r="E162">
-        <f>A162-C162</f>
-        <v>-1.2834472656199978</v>
-      </c>
-      <c r="F162">
-        <f>B162-D162</f>
-        <v>-0.18858337402340197</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B163">
-        <v>48</v>
-      </c>
-      <c r="C163">
-        <v>1213.283203125</v>
-      </c>
-      <c r="D163">
-        <v>48.192241668701101</v>
-      </c>
-      <c r="E163">
-        <f>A163-C163</f>
-        <v>-1.283203125</v>
-      </c>
-      <c r="F163">
-        <f>B163-D163</f>
-        <v>-0.19224166870110082</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B164">
-        <v>48</v>
-      </c>
-      <c r="C164">
-        <v>1213.13940429687</v>
-      </c>
-      <c r="D164">
-        <v>48.305282592773402</v>
-      </c>
-      <c r="E164">
-        <f>A164-C164</f>
-        <v>-1.1394042968699978</v>
-      </c>
-      <c r="F164">
-        <f>B164-D164</f>
-        <v>-0.30528259277340197</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B165">
-        <v>48</v>
-      </c>
-      <c r="C165">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D165">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E165">
-        <f>A165-C165</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F165">
-        <f>B165-D165</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B166">
-        <v>48</v>
-      </c>
-      <c r="C166">
-        <v>1213.58129882812</v>
-      </c>
-      <c r="D166">
-        <v>48.510772705078097</v>
-      </c>
-      <c r="E166">
-        <f>A166-C166</f>
-        <v>-1.5812988281199978</v>
-      </c>
-      <c r="F166">
-        <f>B166-D166</f>
-        <v>-0.51077270507809658</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B167">
-        <v>48</v>
-      </c>
-      <c r="C167">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D167">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E167">
-        <f>A167-C167</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F167">
-        <f>B167-D167</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B168">
-        <v>48</v>
-      </c>
-      <c r="C168">
-        <v>1213.13952636718</v>
-      </c>
-      <c r="D168">
-        <v>48.301563262939403</v>
-      </c>
-      <c r="E168">
-        <f>A168-C168</f>
-        <v>-1.1395263671799967</v>
-      </c>
-      <c r="F168">
-        <f>B168-D168</f>
-        <v>-0.30156326293940339</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B169">
-        <v>48</v>
-      </c>
-      <c r="C169">
-        <v>1212.57202148437</v>
-      </c>
-      <c r="D169">
-        <v>48.134532928466797</v>
-      </c>
-      <c r="E169">
-        <f>A169-C169</f>
-        <v>-0.57202148436999778</v>
-      </c>
-      <c r="F169">
-        <f>B169-D169</f>
-        <v>-0.13453292846679688</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B170">
-        <v>48</v>
-      </c>
-      <c r="C170">
-        <v>1213.54968261718</v>
-      </c>
-      <c r="D170">
-        <v>48.195144653320298</v>
-      </c>
-      <c r="E170">
-        <f>A170-C170</f>
-        <v>-1.5496826171799967</v>
-      </c>
-      <c r="F170">
-        <f>B170-D170</f>
-        <v>-0.19514465332029829</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B171">
-        <v>48</v>
-      </c>
-      <c r="C171">
-        <v>1213.55151367187</v>
-      </c>
-      <c r="D171">
-        <v>48.195228576660099</v>
-      </c>
-      <c r="E171">
-        <f>A171-C171</f>
-        <v>-1.5515136718699978</v>
-      </c>
-      <c r="F171">
-        <f>B171-D171</f>
-        <v>-0.19522857666009941</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B172">
-        <v>48</v>
-      </c>
-      <c r="C172">
-        <v>1213.28344726562</v>
-      </c>
-      <c r="D172">
-        <v>48.188583374023402</v>
-      </c>
-      <c r="E172">
-        <f>A172-C172</f>
-        <v>-1.2834472656199978</v>
-      </c>
-      <c r="F172">
-        <f>B172-D172</f>
-        <v>-0.18858337402340197</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B173">
-        <v>48</v>
-      </c>
-      <c r="C173">
-        <v>1213.11877441406</v>
-      </c>
-      <c r="D173">
-        <v>48.576667785644503</v>
-      </c>
-      <c r="E173">
-        <f>A173-C173</f>
-        <v>-1.1187744140599989</v>
-      </c>
-      <c r="F173">
-        <f>B173-D173</f>
-        <v>-0.57666778564450283</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A174">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B174">
-        <v>48</v>
-      </c>
-      <c r="C174">
-        <v>1213.52893066406</v>
-      </c>
-      <c r="D174">
-        <v>48.470039367675703</v>
-      </c>
-      <c r="E174">
-        <f>A174-C174</f>
-        <v>-1.5289306640599989</v>
-      </c>
-      <c r="F174">
-        <f>B174-D174</f>
-        <v>-0.47003936767570309</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A175">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B175">
-        <v>48</v>
-      </c>
-      <c r="C175">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D175">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E175">
-        <f>A175-C175</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F175">
-        <f>B175-D175</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A176">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B176">
-        <v>48</v>
-      </c>
-      <c r="C176">
-        <v>1213.54968261718</v>
-      </c>
-      <c r="D176">
-        <v>48.195144653320298</v>
-      </c>
-      <c r="E176">
-        <f>A176-C176</f>
-        <v>-1.5496826171799967</v>
-      </c>
-      <c r="F176">
-        <f>B176-D176</f>
-        <v>-0.19514465332029829</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B177">
-        <v>48</v>
-      </c>
-      <c r="C177">
-        <v>1213.30224609375</v>
-      </c>
-      <c r="D177">
-        <v>47.913726806640597</v>
-      </c>
-      <c r="E177">
-        <f>A177-C177</f>
-        <v>-1.30224609375</v>
-      </c>
-      <c r="F177">
-        <f>B177-D177</f>
-        <v>8.6273193359403422E-2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A178">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B178">
-        <v>48</v>
-      </c>
-      <c r="C178">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D178">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E178">
-        <f>A178-C178</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F178">
-        <f>B178-D178</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B179">
-        <v>48</v>
-      </c>
-      <c r="C179">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D179">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E179">
-        <f>A179-C179</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F179">
-        <f>B179-D179</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B180">
-        <v>48</v>
-      </c>
-      <c r="C180">
-        <v>1213.15686035156</v>
-      </c>
-      <c r="D180">
-        <v>48.544288635253899</v>
-      </c>
-      <c r="E180">
-        <f>A180-C180</f>
-        <v>-1.1568603515599989</v>
-      </c>
-      <c r="F180">
-        <f>B180-D180</f>
-        <v>-0.54428863525389914</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A181">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B181">
-        <v>48</v>
-      </c>
-      <c r="C181">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D181">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E181">
-        <f>A181-C181</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F181">
-        <f>B181-D181</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B182">
-        <v>48</v>
-      </c>
-      <c r="C182">
-        <v>1213.53063964843</v>
-      </c>
-      <c r="D182">
-        <v>48.473655700683501</v>
-      </c>
-      <c r="E182">
-        <f>A182-C182</f>
-        <v>-1.5306396484299967</v>
-      </c>
-      <c r="F182">
-        <f>B182-D182</f>
-        <v>-0.47365570068350138</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B183">
-        <v>48</v>
-      </c>
-      <c r="C183">
-        <v>1212.8212890625</v>
-      </c>
-      <c r="D183">
-        <v>48.419334411621001</v>
-      </c>
-      <c r="E183">
-        <f>A183-C183</f>
-        <v>-0.8212890625</v>
-      </c>
-      <c r="F183">
-        <f>B183-D183</f>
-        <v>-0.41933441162100138</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B184">
-        <v>48</v>
-      </c>
-      <c r="C184">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D184">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E184">
-        <f>A184-C184</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F184">
-        <f>B184-D184</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B185">
-        <v>48</v>
-      </c>
-      <c r="C185">
-        <v>1213.55102539062</v>
-      </c>
-      <c r="D185">
-        <v>47.460643768310497</v>
-      </c>
-      <c r="E185">
-        <f>A185-C185</f>
-        <v>-1.5510253906199978</v>
-      </c>
-      <c r="F185">
-        <f>B185-D185</f>
-        <v>0.53935623168950286</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B186">
-        <v>48</v>
-      </c>
-      <c r="C186">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D186">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E186">
-        <f>A186-C186</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F186">
-        <f>B186-D186</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B187">
-        <v>48</v>
-      </c>
-      <c r="C187">
-        <v>1213.12048339843</v>
-      </c>
-      <c r="D187">
-        <v>48.580291748046797</v>
-      </c>
-      <c r="E187">
-        <f>A187-C187</f>
-        <v>-1.1204833984299967</v>
-      </c>
-      <c r="F187">
-        <f>B187-D187</f>
-        <v>-0.58029174804679684</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B188">
-        <v>48</v>
-      </c>
-      <c r="C188">
-        <v>1213.53063964843</v>
-      </c>
-      <c r="D188">
-        <v>48.473655700683501</v>
-      </c>
-      <c r="E188">
-        <f>A188-C188</f>
-        <v>-1.5306396484299967</v>
-      </c>
-      <c r="F188">
-        <f>B188-D188</f>
-        <v>-0.47365570068350138</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A189">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B189">
-        <v>48</v>
-      </c>
-      <c r="C189">
-        <v>1213.12048339843</v>
-      </c>
-      <c r="D189">
-        <v>48.580291748046797</v>
-      </c>
-      <c r="E189">
-        <f>A189-C189</f>
-        <v>-1.1204833984299967</v>
-      </c>
-      <c r="F189">
-        <f>B189-D189</f>
-        <v>-0.58029174804679684</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B190">
-        <v>48</v>
-      </c>
-      <c r="C190">
-        <v>1213.24365234375</v>
-      </c>
-      <c r="D190">
-        <v>48.741989135742102</v>
-      </c>
-      <c r="E190">
-        <f>A190-C190</f>
-        <v>-1.24365234375</v>
-      </c>
-      <c r="F190">
-        <f>B190-D190</f>
-        <v>-0.74198913574210223</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191">
-        <f>1260-48</f>
-        <v>1212</v>
-      </c>
-      <c r="B191">
-        <v>48</v>
-      </c>
-      <c r="C191">
-        <v>1213.26440429687</v>
-      </c>
-      <c r="D191">
-        <v>48.467094421386697</v>
-      </c>
-      <c r="E191">
-        <f>A191-C191</f>
-        <v>-1.2644042968699978</v>
-      </c>
-      <c r="F191">
-        <f>B191-D191</f>
-        <v>-0.46709442138669743</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6B512F-7C6F-4CE4-8B45-AB8D7FB88A15}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <f>A3*420</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f>B3*297</f>
-        <v>297</v>
-      </c>
-      <c r="E3">
-        <v>46.319923400878899</v>
-      </c>
-      <c r="F3">
-        <v>345.10632324218699</v>
-      </c>
-      <c r="G3">
-        <f>E3-48</f>
-        <v>-1.6800765991211009</v>
-      </c>
-      <c r="H3">
-        <f>F3-48</f>
-        <v>297.10632324218699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <f>A4*420</f>
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f>B4*297</f>
-        <v>297</v>
-      </c>
-      <c r="E4">
-        <v>46.578781127929602</v>
-      </c>
-      <c r="F4">
-        <v>344.84744262695301</v>
-      </c>
-      <c r="G4">
-        <f>E4-48</f>
-        <v>-1.4212188720703978</v>
-      </c>
-      <c r="H4">
-        <f>F4-48</f>
-        <v>296.84744262695301</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <f>A5*420</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f>B5*297</f>
-        <v>297</v>
-      </c>
-      <c r="E5">
-        <v>46.578781127929602</v>
-      </c>
-      <c r="F5">
-        <v>344.84744262695301</v>
-      </c>
-      <c r="G5">
-        <f>E5-48</f>
-        <v>-1.4212188720703978</v>
-      </c>
-      <c r="H5">
-        <f>F5-48</f>
-        <v>296.84744262695301</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <f>A6*420</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f>B6*297</f>
-        <v>297</v>
-      </c>
-      <c r="E6">
-        <v>46.319923400878899</v>
-      </c>
-      <c r="F6">
-        <v>345.10632324218699</v>
-      </c>
-      <c r="G6">
-        <f>E6-48</f>
-        <v>-1.6800765991211009</v>
-      </c>
-      <c r="H6">
-        <f>F6-48</f>
-        <v>297.10632324218699</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <f>A7*420</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <f>B7*297</f>
-        <v>297</v>
-      </c>
-      <c r="E7">
-        <v>46.048778533935497</v>
-      </c>
-      <c r="F7">
-        <v>344.57034301757801</v>
-      </c>
-      <c r="G7">
-        <f>E7-48</f>
-        <v>-1.9512214660645029</v>
-      </c>
-      <c r="H7">
-        <f>F7-48</f>
-        <v>296.57034301757801</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <f>A8*420</f>
-        <v>420</v>
-      </c>
-      <c r="D8">
-        <f>B8*297</f>
-        <v>297</v>
-      </c>
-      <c r="E8">
-        <v>467.43136596679602</v>
-      </c>
-      <c r="F8">
-        <v>344.59210205078102</v>
-      </c>
-      <c r="G8">
-        <f>E8-48</f>
-        <v>419.43136596679602</v>
-      </c>
-      <c r="H8">
-        <f>F8-48</f>
-        <v>296.59210205078102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <f>A9*420</f>
-        <v>420</v>
-      </c>
-      <c r="D9">
-        <f>B9*297</f>
-        <v>297</v>
-      </c>
-      <c r="E9">
-        <v>467.4345703125</v>
-      </c>
-      <c r="F9">
-        <v>344.324615478515</v>
-      </c>
-      <c r="G9">
-        <f>E9-48</f>
-        <v>419.4345703125</v>
-      </c>
-      <c r="H9">
-        <f>F9-48</f>
-        <v>296.324615478515</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <f>A10*420</f>
-        <v>420</v>
-      </c>
-      <c r="D10">
-        <f>B10*297</f>
-        <v>297</v>
-      </c>
-      <c r="E10">
-        <v>467.16867065429602</v>
-      </c>
-      <c r="F10">
-        <v>344.57995605468699</v>
-      </c>
-      <c r="G10">
-        <f>E10-48</f>
-        <v>419.16867065429602</v>
-      </c>
-      <c r="H10">
-        <f>F10-48</f>
-        <v>296.57995605468699</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <f>A11*420</f>
-        <v>420</v>
-      </c>
-      <c r="D11">
-        <f>B11*297</f>
-        <v>297</v>
-      </c>
-      <c r="E11">
-        <v>467.16354370117102</v>
-      </c>
-      <c r="F11">
-        <v>344.84747314453102</v>
-      </c>
-      <c r="G11">
-        <f>E11-48</f>
-        <v>419.16354370117102</v>
-      </c>
-      <c r="H11">
-        <f>F11-48</f>
-        <v>296.84747314453102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <f>A12*420</f>
-        <v>420</v>
-      </c>
-      <c r="D12">
-        <f>B12*297</f>
-        <v>297</v>
-      </c>
-      <c r="E12">
-        <v>467.16354370117102</v>
-      </c>
-      <c r="F12">
-        <v>344.84747314453102</v>
-      </c>
-      <c r="G12">
-        <f>E12-48</f>
-        <v>419.16354370117102</v>
-      </c>
-      <c r="H12">
-        <f>F12-48</f>
-        <v>296.84747314453102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <f>A13*420</f>
-        <v>840</v>
-      </c>
-      <c r="D13">
-        <f>B13*297</f>
-        <v>297</v>
-      </c>
-      <c r="E13">
-        <v>885.40826416015602</v>
-      </c>
-      <c r="F13">
-        <v>345.08062744140602</v>
-      </c>
-      <c r="G13">
-        <f>E13-48</f>
-        <v>837.40826416015602</v>
-      </c>
-      <c r="H13">
-        <f>F13-48</f>
-        <v>297.08062744140602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <f>A14*420</f>
-        <v>840</v>
-      </c>
-      <c r="D14">
-        <f>B14*297</f>
-        <v>297</v>
-      </c>
-      <c r="E14">
-        <v>885.40826416015602</v>
-      </c>
-      <c r="F14">
-        <v>345.08062744140602</v>
-      </c>
-      <c r="G14">
-        <f>E14-48</f>
-        <v>837.40826416015602</v>
-      </c>
-      <c r="H14">
-        <f>F14-48</f>
-        <v>297.08062744140602</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <f>A15*420</f>
-        <v>840</v>
-      </c>
-      <c r="D15">
-        <f>B15*297</f>
-        <v>297</v>
-      </c>
-      <c r="E15">
-        <v>884.88427734375</v>
-      </c>
-      <c r="F15">
-        <v>345.07464599609301</v>
-      </c>
-      <c r="G15">
-        <f>E15-48</f>
-        <v>836.88427734375</v>
-      </c>
-      <c r="H15">
-        <f>F15-48</f>
-        <v>297.07464599609301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <f>A16*420</f>
-        <v>840</v>
-      </c>
-      <c r="D16">
-        <f>B16*297</f>
-        <v>297</v>
-      </c>
-      <c r="E16">
-        <v>885.4208984375</v>
-      </c>
-      <c r="F16">
-        <v>344.81701660156199</v>
-      </c>
-      <c r="G16">
-        <f>E16-48</f>
-        <v>837.4208984375</v>
-      </c>
-      <c r="H16">
-        <f>F16-48</f>
-        <v>296.81701660156199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <f>A17*420</f>
-        <v>840</v>
-      </c>
-      <c r="D17">
-        <f>B17*297</f>
-        <v>297</v>
-      </c>
-      <c r="E17">
-        <v>885.67108154296795</v>
-      </c>
-      <c r="F17">
-        <v>345.08538818359301</v>
-      </c>
-      <c r="G17">
-        <f>E17-48</f>
-        <v>837.67108154296795</v>
-      </c>
-      <c r="H17">
-        <f>F17-48</f>
-        <v>297.08538818359301</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>0</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <f>A18*420</f>
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <f>B18*297</f>
-        <v>594</v>
-      </c>
-      <c r="E18">
-        <v>47.272800445556598</v>
-      </c>
-      <c r="F18">
-        <v>640.40020751953102</v>
-      </c>
-      <c r="G18">
-        <f>E18-48</f>
-        <v>-0.72719955444340201</v>
-      </c>
-      <c r="H18">
-        <f>F18-48</f>
-        <v>592.40020751953102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <f>A19*420</f>
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <f>B19*297</f>
-        <v>594</v>
-      </c>
-      <c r="E19">
-        <v>47.0185546875</v>
-      </c>
-      <c r="F19">
-        <v>640.65252685546795</v>
-      </c>
-      <c r="G19">
-        <f>E19-48</f>
-        <v>-0.9814453125</v>
-      </c>
-      <c r="H19">
-        <f>F19-48</f>
-        <v>592.65252685546795</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <f>A20*420</f>
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <f>B20*297</f>
-        <v>594</v>
-      </c>
-      <c r="E20">
-        <v>47.5253295898437</v>
-      </c>
-      <c r="F20">
-        <v>640.151123046875</v>
-      </c>
-      <c r="G20">
-        <f>E20-48</f>
-        <v>-0.47467041015629974</v>
-      </c>
-      <c r="H20">
-        <f>F20-48</f>
-        <v>592.151123046875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>0</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <f>A21*420</f>
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <f>B21*297</f>
-        <v>594</v>
-      </c>
-      <c r="E21">
-        <v>47.27534866333</v>
-      </c>
-      <c r="F21">
-        <v>640.65716552734295</v>
-      </c>
-      <c r="G21">
-        <f>E21-48</f>
-        <v>-0.72465133667000003</v>
-      </c>
-      <c r="H21">
-        <f>F21-48</f>
-        <v>592.65716552734295</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <f>A22*420</f>
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <f>B22*297</f>
-        <v>594</v>
-      </c>
-      <c r="E22">
-        <v>47.27534866333</v>
-      </c>
-      <c r="F22">
-        <v>640.65716552734295</v>
-      </c>
-      <c r="G22">
-        <f>E22-48</f>
-        <v>-0.72465133667000003</v>
-      </c>
-      <c r="H22">
-        <f>F22-48</f>
-        <v>592.65716552734295</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <f>A23*420</f>
-        <v>420</v>
-      </c>
-      <c r="D23">
-        <f>B23*297</f>
-        <v>594</v>
-      </c>
-      <c r="E23">
-        <v>465.253173828125</v>
-      </c>
-      <c r="F23">
-        <v>640.733154296875</v>
-      </c>
-      <c r="G23">
-        <f>E23-48</f>
-        <v>417.253173828125</v>
-      </c>
-      <c r="H23">
-        <f>F23-48</f>
-        <v>592.733154296875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <f>A24*420</f>
-        <v>420</v>
-      </c>
-      <c r="D24">
-        <f>B24*297</f>
-        <v>594</v>
-      </c>
-      <c r="E24">
-        <v>464.99578857421801</v>
-      </c>
-      <c r="F24">
-        <v>640.72344970703102</v>
-      </c>
-      <c r="G24">
-        <f>E24-48</f>
-        <v>416.99578857421801</v>
-      </c>
-      <c r="H24">
-        <f>F24-48</f>
-        <v>592.72344970703102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <f>A25*420</f>
-        <v>420</v>
-      </c>
-      <c r="D25">
-        <f>B25*297</f>
-        <v>594</v>
-      </c>
-      <c r="E25">
-        <v>464.74499511718699</v>
-      </c>
-      <c r="F25">
-        <v>640.464111328125</v>
-      </c>
-      <c r="G25">
-        <f>E25-48</f>
-        <v>416.74499511718699</v>
-      </c>
-      <c r="H25">
-        <f>F25-48</f>
-        <v>592.464111328125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>1</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <f>A26*420</f>
-        <v>420</v>
-      </c>
-      <c r="D26">
-        <f>B26*297</f>
-        <v>594</v>
-      </c>
-      <c r="E26">
-        <v>465.25149536132801</v>
-      </c>
-      <c r="F26">
-        <v>640.729736328125</v>
-      </c>
-      <c r="G26">
-        <f>E26-48</f>
-        <v>417.25149536132801</v>
-      </c>
-      <c r="H26">
-        <f>F26-48</f>
-        <v>592.729736328125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <f>A27*420</f>
-        <v>420</v>
-      </c>
-      <c r="D27">
-        <f>B27*297</f>
-        <v>594</v>
-      </c>
-      <c r="E27">
-        <v>464.98919677734301</v>
-      </c>
-      <c r="F27">
-        <v>640.97991943359295</v>
-      </c>
-      <c r="G27">
-        <f>E27-48</f>
-        <v>416.98919677734301</v>
-      </c>
-      <c r="H27">
-        <f>F27-48</f>
-        <v>592.97991943359295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>2</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28">
-        <f>A28*420</f>
-        <v>840</v>
-      </c>
-      <c r="D28">
-        <f>B28*297</f>
-        <v>594</v>
-      </c>
-      <c r="E28">
-        <v>886.680908203125</v>
-      </c>
-      <c r="F28">
-        <v>642.23931884765602</v>
-      </c>
-      <c r="G28">
-        <f>E28-48</f>
-        <v>838.680908203125</v>
-      </c>
-      <c r="H28">
-        <f>F28-48</f>
-        <v>594.23931884765602</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-      <c r="C29">
-        <f>A29*420</f>
-        <v>840</v>
-      </c>
-      <c r="D29">
-        <f>B29*297</f>
-        <v>594</v>
-      </c>
-      <c r="E29">
-        <v>886.96484375</v>
-      </c>
-      <c r="F29">
-        <v>641.73724365234295</v>
-      </c>
-      <c r="G29">
-        <f>E29-48</f>
-        <v>838.96484375</v>
-      </c>
-      <c r="H29">
-        <f>F29-48</f>
-        <v>593.73724365234295</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30">
-        <f>A30*420</f>
-        <v>840</v>
-      </c>
-      <c r="D30">
-        <f>B30*297</f>
-        <v>594</v>
-      </c>
-      <c r="E30">
-        <v>886.42510986328102</v>
-      </c>
-      <c r="F30">
-        <v>642.23248291015602</v>
-      </c>
-      <c r="G30">
-        <f>E30-48</f>
-        <v>838.42510986328102</v>
-      </c>
-      <c r="H30">
-        <f>F30-48</f>
-        <v>594.23248291015602</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31">
-        <v>2</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31">
-        <f>A31*420</f>
-        <v>840</v>
-      </c>
-      <c r="D31">
-        <f>B31*297</f>
-        <v>594</v>
-      </c>
-      <c r="E31">
-        <v>886.42333984375</v>
-      </c>
-      <c r="F31">
-        <v>642.232421875</v>
-      </c>
-      <c r="G31">
-        <f>E31-48</f>
-        <v>838.42333984375</v>
-      </c>
-      <c r="H31">
-        <f>F31-48</f>
-        <v>594.232421875</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <f>A32*420</f>
-        <v>840</v>
-      </c>
-      <c r="D32">
-        <f>B32*297</f>
-        <v>594</v>
-      </c>
-      <c r="E32">
-        <v>886.42333984375</v>
-      </c>
-      <c r="F32">
-        <v>642.232421875</v>
-      </c>
-      <c r="G32">
-        <f>E32-48</f>
-        <v>838.42333984375</v>
-      </c>
-      <c r="H32">
-        <f>F32-48</f>
-        <v>594.232421875</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>